--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrWtFxswap.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrWtFxswap.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ideaworkspaces\ZGBS-CP-dev\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -76,11 +76,11 @@
     <t>已完成额度</t>
   </si>
   <si>
-    <t>交易完成度(%)</t>
+    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>备注</t>
+    <t>交易完成度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,10 +505,10 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.15">
